--- a/Solar 2010 - 2012.xlsx
+++ b/Solar 2010 - 2012.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfc87df69086cb6c/Desktop/Green Bonds Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="230" documentId="11_F25DC773A252ABDACC104822D1DA4E065ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{216F19F3-64A5-457B-9258-27731F0FF7D1}"/>
+  <xr:revisionPtr revIDLastSave="261" documentId="11_F25DC773A252ABDACC104822D1DA4E065ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F3B1600-62D4-451F-A9A6-CBFAB1FAF49E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Alabama</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>Year 2012</t>
+  </si>
+  <si>
+    <t>Year 2013</t>
   </si>
 </sst>
 </file>
@@ -522,14 +525,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="9.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -542,8 +545,11 @@
       <c r="D1" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -556,8 +562,11 @@
       <c r="D2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -570,8 +579,11 @@
       <c r="D3">
         <v>284</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -584,8 +596,11 @@
       <c r="D4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -598,8 +613,11 @@
       <c r="D5">
         <v>256</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -612,8 +630,11 @@
       <c r="D6">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -626,8 +647,11 @@
       <c r="D7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -640,8 +664,11 @@
       <c r="D8">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -654,8 +681,11 @@
       <c r="D9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -668,8 +698,11 @@
       <c r="D10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -682,8 +715,11 @@
       <c r="D11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -696,8 +732,11 @@
       <c r="D12">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -710,8 +749,11 @@
       <c r="D13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E13">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -724,8 +766,11 @@
       <c r="D14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -738,8 +783,11 @@
       <c r="D15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -752,8 +800,11 @@
       <c r="D16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -766,8 +817,11 @@
       <c r="D17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -780,8 +834,11 @@
       <c r="D18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -794,8 +851,11 @@
       <c r="D19">
         <v>39</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -808,8 +868,11 @@
       <c r="D20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -822,8 +885,11 @@
       <c r="D21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -836,8 +902,11 @@
       <c r="D22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -850,8 +919,11 @@
       <c r="D23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -864,8 +936,11 @@
       <c r="D24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -878,8 +953,11 @@
       <c r="D25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -892,8 +970,11 @@
       <c r="D26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -906,8 +987,11 @@
       <c r="D27">
         <v>186</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -921,7 +1005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -934,8 +1018,11 @@
       <c r="D29">
         <v>27</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -948,8 +1035,11 @@
       <c r="D30">
         <v>22</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -962,8 +1052,11 @@
       <c r="D31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -976,8 +1069,11 @@
       <c r="D32">
         <v>33</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E32">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -990,8 +1086,11 @@
       <c r="D33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -1004,8 +1103,11 @@
       <c r="D34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -1018,8 +1120,11 @@
       <c r="D35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -1032,8 +1137,11 @@
       <c r="D36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -1046,8 +1154,11 @@
       <c r="D37">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -1060,8 +1171,11 @@
       <c r="D38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -1074,8 +1188,11 @@
       <c r="D39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -1088,8 +1205,11 @@
       <c r="D40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -1102,8 +1222,11 @@
       <c r="D41">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -1116,8 +1239,11 @@
       <c r="D42">
         <v>30</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E42">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -1130,8 +1256,11 @@
       <c r="D43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -1144,8 +1273,11 @@
       <c r="D44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -1158,8 +1290,11 @@
       <c r="D45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -1172,8 +1307,11 @@
       <c r="D46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -1186,8 +1324,11 @@
       <c r="D47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -1200,8 +1341,11 @@
       <c r="D48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -1212,6 +1356,9 @@
         <v>0</v>
       </c>
       <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
         <v>0</v>
       </c>
     </row>
